--- a/Design Files/Sensor Board - v1.0/BOM/Client_BOM_Sensor_Board-v1.0.xlsx
+++ b/Design Files/Sensor Board - v1.0/BOM/Client_BOM_Sensor_Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="127">
   <si>
     <t>#</t>
   </si>
@@ -388,13 +388,25 @@
   </si>
   <si>
     <t>Custom</t>
+  </si>
+  <si>
+    <t>Pripheral</t>
+  </si>
+  <si>
+    <t>Original Panasonic CR2477 battery CR 2477 instrument meter imported digital tire pressure monitor intelligent toilet</t>
+  </si>
+  <si>
+    <t>CR2477</t>
+  </si>
+  <si>
+    <t>Panasonic</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -449,6 +461,21 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -569,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -606,9 +633,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -616,6 +640,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -905,7 +941,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
@@ -929,9 +965,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1001,7 +1037,7 @@
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B24" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B25" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
@@ -1103,28 +1139,28 @@
       <c r="C7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="14">
         <v>2</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="16" t="s">
         <v>120</v>
       </c>
     </row>
@@ -1169,28 +1205,28 @@
       <c r="C9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="14">
         <v>2</v>
       </c>
-      <c r="K9" s="17" t="s">
+      <c r="K9" s="16" t="s">
         <v>120</v>
       </c>
     </row>
@@ -1297,28 +1333,28 @@
       <c r="C13" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="J13" s="15">
-        <v>1</v>
-      </c>
-      <c r="K13" s="17" t="s">
+      <c r="J13" s="14">
+        <v>1</v>
+      </c>
+      <c r="K13" s="16" t="s">
         <v>120</v>
       </c>
     </row>
@@ -1491,28 +1527,28 @@
       <c r="C19" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="I19" s="16" t="s">
+      <c r="I19" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="J19" s="15">
-        <v>1</v>
-      </c>
-      <c r="K19" s="17" t="s">
+      <c r="J19" s="14">
+        <v>1</v>
+      </c>
+      <c r="K19" s="16" t="s">
         <v>120</v>
       </c>
     </row>
@@ -1653,30 +1689,61 @@
       <c r="C24" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="H24" s="15" t="s">
+      <c r="H24" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="I24" s="16" t="s">
+      <c r="I24" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="J24" s="15">
-        <v>1</v>
-      </c>
-      <c r="K24" s="17" t="s">
+      <c r="J24" s="14">
+        <v>1</v>
+      </c>
+      <c r="K24" s="16" t="s">
         <v>120</v>
       </c>
+    </row>
+    <row r="25" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="11">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I25" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="J25" s="18">
+        <v>1</v>
+      </c>
+      <c r="K25" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
